--- a/老虎机数学入门-PartII-免费游戏RTP模型.xlsx
+++ b/老虎机数学入门-PartII-免费游戏RTP模型.xlsx
@@ -7120,6 +7120,9 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:R166" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -15711,5 +15714,8 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:P250" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/老虎机数学入门-PartII-免费游戏RTP模型.xlsx
+++ b/老虎机数学入门-PartII-免费游戏RTP模型.xlsx
@@ -10,7 +10,7 @@
     <sheet name="说明" sheetId="1" r:id="rId1"/>
     <sheet name="PartII 主游戏+免费游戏→RTP汇总" sheetId="6" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3351" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3176" uniqueCount="248">
   <si>
     <t>老虎机数学入门 PART Ⅱ —— 免费游戏 / 再触发 RTP 计算模型</t>
   </si>
@@ -1030,13 +1030,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="6">
+  <numFmts count="8">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.00000000"/>
     <numFmt numFmtId="177" formatCode="0.0000"/>
+    <numFmt numFmtId="178" formatCode="0.00%"/>
+    <numFmt numFmtId="179" formatCode="0.0000%"/>
   </numFmts>
   <fonts count="37">
     <font>
@@ -1774,7 +1776,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1863,6 +1865,41 @@
     <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -3234,3842 +3271,3842 @@
       </c>
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:10">
-      <c r="A27" s="36" t="s">
+      <c r="A27" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="B27" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C27" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D27" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E27" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F27" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G27" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H27" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I27" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J27" s="37" t="s">
+      <c r="B27" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C27" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D27" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E27" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G27" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H27" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I27" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J27" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="B28" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D28" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E28" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F28" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G28" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H28" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I28" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J28" s="37" t="s">
+      <c r="A28" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="B28" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D28" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E28" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G28" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H28" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I28" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J28" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" ht="16.5" spans="1:10">
-      <c r="A29" s="39" t="s">
+      <c r="A29" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="B29" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C29" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D29" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E29" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F29" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G29" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H29" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I29" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J29" s="37" t="s">
+      <c r="B29" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C29" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D29" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E29" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G29" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H29" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I29" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J29" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="30" ht="16.5" spans="1:10">
-      <c r="A30" s="39" t="s">
+      <c r="A30" s="52" t="s">
         <v>22</v>
       </c>
-      <c r="B30" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C30" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D30" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E30" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F30" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G30" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H30" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I30" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J30" s="37" t="s">
+      <c r="B30" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C30" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D30" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E30" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G30" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H30" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I30" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J30" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="31" ht="16.5" spans="1:10">
-      <c r="A31" s="39" t="s">
+      <c r="A31" s="52" t="s">
         <v>23</v>
       </c>
-      <c r="B31" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C31" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D31" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E31" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F31" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G31" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H31" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I31" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J31" s="37" t="s">
+      <c r="B31" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C31" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D31" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E31" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G31" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H31" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I31" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J31" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="32" ht="16.5" spans="1:10">
-      <c r="A32" s="39" t="s">
+      <c r="A32" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="B32" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C32" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D32" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E32" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F32" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G32" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H32" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I32" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J32" s="37" t="s">
+      <c r="B32" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C32" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D32" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E32" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G32" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H32" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I32" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J32" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1" spans="1:10">
-      <c r="A33" s="40" t="s">
+      <c r="A33" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="B33" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C33" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D33" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E33" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F33" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G33" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H33" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I33" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J33" s="37" t="s">
+      <c r="B33" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C33" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D33" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E33" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G33" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H33" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I33" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J33" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:10">
-      <c r="A34" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="B34" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C34" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D34" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E34" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F34" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G34" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H34" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I34" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J34" s="37" t="s">
+      <c r="A34" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="B34" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C34" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D34" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E34" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G34" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H34" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I34" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J34" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="35" ht="16.5" spans="1:10">
-      <c r="A35" s="41" t="s">
+      <c r="A35" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="B35" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C35" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D35" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E35" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F35" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G35" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H35" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I35" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J35" s="37" t="s">
+      <c r="B35" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C35" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D35" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E35" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G35" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H35" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I35" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J35" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1" spans="1:10">
-      <c r="A36" s="42" t="s">
+      <c r="A36" s="55" t="s">
         <v>27</v>
       </c>
-      <c r="B36" s="43" t="s">
+      <c r="B36" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="C36" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D36" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E36" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F36" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G36" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H36" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I36" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J36" s="37" t="s">
+      <c r="C36" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D36" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E36" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G36" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H36" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I36" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J36" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" ht="14.5" spans="1:10">
-      <c r="A37" s="44" t="s">
+      <c r="A37" s="57" t="s">
         <v>29</v>
       </c>
-      <c r="B37" s="45" t="s">
+      <c r="B37" s="58" t="s">
         <v>30</v>
       </c>
-      <c r="C37" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D37" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E37" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F37" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G37" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H37" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I37" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J37" s="37" t="s">
+      <c r="C37" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D37" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E37" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G37" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H37" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I37" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J37" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="38" ht="14.5" spans="1:10">
-      <c r="A38" s="44" t="s">
+      <c r="A38" s="57" t="s">
         <v>31</v>
       </c>
-      <c r="B38" s="45" t="s">
+      <c r="B38" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="C38" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D38" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E38" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F38" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G38" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H38" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I38" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J38" s="37" t="s">
+      <c r="C38" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D38" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E38" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G38" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H38" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I38" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J38" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="39" ht="14.5" spans="1:10">
-      <c r="A39" s="44" t="s">
+      <c r="A39" s="57" t="s">
         <v>33</v>
       </c>
-      <c r="B39" s="45" t="s">
+      <c r="B39" s="58" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D39" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E39" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F39" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G39" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H39" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I39" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J39" s="37" t="s">
+      <c r="C39" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D39" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E39" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G39" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H39" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I39" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J39" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="40" ht="14.5" spans="1:10">
-      <c r="A40" s="44" t="s">
+      <c r="A40" s="57" t="s">
         <v>35</v>
       </c>
-      <c r="B40" s="45" t="s">
+      <c r="B40" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="C40" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D40" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E40" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F40" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G40" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H40" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I40" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J40" s="37" t="s">
+      <c r="C40" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D40" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E40" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G40" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H40" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I40" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J40" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:10">
-      <c r="A41" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="B41" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C41" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D41" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E41" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F41" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G41" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H41" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I41" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J41" s="37" t="s">
+      <c r="A41" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="B41" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C41" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D41" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E41" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G41" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H41" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I41" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J41" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="42" ht="16.5" spans="1:10">
-      <c r="A42" s="41" t="s">
+      <c r="A42" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="B42" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C42" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D42" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E42" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F42" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G42" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H42" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I42" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J42" s="37" t="s">
+      <c r="B42" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C42" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D42" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E42" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G42" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H42" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I42" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J42" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="43" ht="16.5" spans="1:10">
-      <c r="A43" s="41" t="s">
+      <c r="A43" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="B43" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C43" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D43" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E43" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F43" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G43" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H43" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I43" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J43" s="37" t="s">
+      <c r="B43" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C43" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D43" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E43" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G43" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H43" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I43" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J43" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="1:10">
-      <c r="A44" s="41" t="s">
+      <c r="A44" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="B44" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C44" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D44" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E44" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F44" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G44" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H44" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I44" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J44" s="37" t="s">
+      <c r="B44" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C44" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D44" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E44" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G44" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H44" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I44" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J44" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" ht="16.5" spans="1:10">
-      <c r="A45" s="41" t="s">
+      <c r="A45" s="54" t="s">
         <v>40</v>
       </c>
-      <c r="B45" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C45" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D45" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E45" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F45" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G45" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H45" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I45" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J45" s="37" t="s">
+      <c r="B45" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C45" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D45" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E45" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G45" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H45" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I45" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J45" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="46" ht="16.5" spans="1:10">
-      <c r="A46" s="41" t="s">
+      <c r="A46" s="54" t="s">
         <v>41</v>
       </c>
-      <c r="B46" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C46" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D46" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E46" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F46" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G46" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H46" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I46" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J46" s="37" t="s">
+      <c r="B46" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C46" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D46" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E46" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G46" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H46" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I46" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J46" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1" spans="1:10">
-      <c r="A47" s="40" t="s">
+      <c r="A47" s="53" t="s">
         <v>42</v>
       </c>
-      <c r="B47" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C47" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D47" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E47" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F47" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G47" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H47" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I47" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J47" s="37" t="s">
+      <c r="B47" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C47" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D47" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E47" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G47" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H47" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I47" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J47" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:10">
-      <c r="A48" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="B48" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C48" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D48" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E48" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F48" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G48" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H48" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I48" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J48" s="37" t="s">
+      <c r="A48" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="B48" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C48" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D48" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E48" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G48" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H48" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I48" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J48" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" ht="16.5" spans="1:10">
-      <c r="A49" s="46" t="s">
+      <c r="A49" s="59" t="s">
         <v>43</v>
       </c>
-      <c r="B49" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C49" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D49" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E49" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F49" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G49" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H49" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I49" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J49" s="37" t="s">
+      <c r="B49" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C49" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D49" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E49" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G49" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H49" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I49" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J49" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="50" ht="16.5" spans="1:10">
-      <c r="A50" s="46" t="s">
+      <c r="A50" s="59" t="s">
         <v>44</v>
       </c>
-      <c r="B50" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C50" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D50" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E50" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F50" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G50" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H50" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I50" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J50" s="37" t="s">
+      <c r="B50" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C50" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D50" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E50" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G50" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H50" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I50" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J50" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="51" ht="16.5" spans="1:10">
-      <c r="A51" s="41" t="s">
+      <c r="A51" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="B51" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C51" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D51" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E51" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F51" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G51" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H51" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I51" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J51" s="37" t="s">
+      <c r="B51" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C51" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D51" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E51" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F51" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G51" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H51" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I51" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J51" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1" spans="1:10">
-      <c r="A52" s="42" t="s">
+      <c r="A52" s="55" t="s">
         <v>46</v>
       </c>
-      <c r="B52" s="43" t="s">
+      <c r="B52" s="56" t="s">
         <v>47</v>
       </c>
-      <c r="C52" s="43" t="s">
+      <c r="C52" s="56" t="s">
         <v>48</v>
       </c>
-      <c r="D52" s="43" t="s">
+      <c r="D52" s="56" t="s">
         <v>49</v>
       </c>
-      <c r="E52" s="43" t="s">
+      <c r="E52" s="56" t="s">
         <v>50</v>
       </c>
-      <c r="F52" s="43" t="s">
+      <c r="F52" s="56" t="s">
         <v>51</v>
       </c>
-      <c r="G52" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H52" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I52" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J52" s="37" t="s">
+      <c r="G52" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H52" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I52" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J52" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" ht="14.5" spans="1:10">
-      <c r="A53" s="44" t="s">
+      <c r="A53" s="57" t="s">
         <v>52</v>
       </c>
-      <c r="B53" s="45" t="s">
-        <v>53</v>
-      </c>
-      <c r="C53" s="45" t="s">
-        <v>53</v>
-      </c>
-      <c r="D53" s="45" t="s">
-        <v>53</v>
-      </c>
-      <c r="E53" s="45" t="s">
-        <v>53</v>
-      </c>
-      <c r="F53" s="45" t="s">
-        <v>53</v>
-      </c>
-      <c r="G53" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H53" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I53" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J53" s="37" t="s">
+      <c r="B53" s="58">
+        <v>20</v>
+      </c>
+      <c r="C53" s="58">
+        <v>20</v>
+      </c>
+      <c r="D53" s="58">
+        <v>20</v>
+      </c>
+      <c r="E53" s="58">
+        <v>20</v>
+      </c>
+      <c r="F53" s="58">
+        <v>20</v>
+      </c>
+      <c r="G53" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H53" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I53" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J53" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="54" ht="14.5" spans="1:10">
-      <c r="A54" s="44" t="s">
+      <c r="A54" s="57" t="s">
         <v>54</v>
       </c>
-      <c r="B54" s="45" t="s">
-        <v>55</v>
-      </c>
-      <c r="C54" s="45" t="s">
-        <v>56</v>
-      </c>
-      <c r="D54" s="45" t="s">
-        <v>56</v>
-      </c>
-      <c r="E54" s="45" t="s">
-        <v>56</v>
-      </c>
-      <c r="F54" s="45" t="s">
-        <v>56</v>
-      </c>
-      <c r="G54" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H54" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I54" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J54" s="37" t="s">
+      <c r="B54" s="58">
+        <v>0</v>
+      </c>
+      <c r="C54" s="58">
+        <v>1</v>
+      </c>
+      <c r="D54" s="58">
+        <v>1</v>
+      </c>
+      <c r="E54" s="58">
+        <v>1</v>
+      </c>
+      <c r="F54" s="58">
+        <v>1</v>
+      </c>
+      <c r="G54" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H54" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I54" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J54" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="55" ht="14.5" spans="1:10">
-      <c r="A55" s="44" t="s">
+      <c r="A55" s="57" t="s">
         <v>57</v>
       </c>
-      <c r="B55" s="45" t="s">
-        <v>56</v>
-      </c>
-      <c r="C55" s="45" t="s">
-        <v>58</v>
-      </c>
-      <c r="D55" s="45" t="s">
-        <v>58</v>
-      </c>
-      <c r="E55" s="45" t="s">
-        <v>58</v>
-      </c>
-      <c r="F55" s="45" t="s">
-        <v>58</v>
-      </c>
-      <c r="G55" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H55" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I55" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J55" s="37" t="s">
+      <c r="B55" s="58">
+        <v>1</v>
+      </c>
+      <c r="C55" s="58">
+        <v>3</v>
+      </c>
+      <c r="D55" s="58">
+        <v>3</v>
+      </c>
+      <c r="E55" s="58">
+        <v>3</v>
+      </c>
+      <c r="F55" s="58">
+        <v>3</v>
+      </c>
+      <c r="G55" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H55" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I55" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J55" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="56" ht="14.5" spans="1:10">
-      <c r="A56" s="44" t="s">
+      <c r="A56" s="57" t="s">
         <v>59</v>
       </c>
-      <c r="B56" s="45" t="s">
-        <v>58</v>
-      </c>
-      <c r="C56" s="45" t="s">
-        <v>58</v>
-      </c>
-      <c r="D56" s="45" t="s">
-        <v>58</v>
-      </c>
-      <c r="E56" s="45" t="s">
-        <v>58</v>
-      </c>
-      <c r="F56" s="45" t="s">
-        <v>58</v>
-      </c>
-      <c r="G56" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H56" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I56" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J56" s="37" t="s">
+      <c r="B56" s="58">
+        <v>3</v>
+      </c>
+      <c r="C56" s="58">
+        <v>3</v>
+      </c>
+      <c r="D56" s="58">
+        <v>3</v>
+      </c>
+      <c r="E56" s="58">
+        <v>3</v>
+      </c>
+      <c r="F56" s="58">
+        <v>3</v>
+      </c>
+      <c r="G56" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H56" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I56" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J56" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" ht="14.5" spans="1:10">
-      <c r="A57" s="44" t="s">
+      <c r="A57" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="B57" s="45" t="s">
-        <v>61</v>
-      </c>
-      <c r="C57" s="45" t="s">
-        <v>62</v>
-      </c>
-      <c r="D57" s="45" t="s">
-        <v>61</v>
-      </c>
-      <c r="E57" s="45" t="s">
-        <v>61</v>
-      </c>
-      <c r="F57" s="45" t="s">
-        <v>61</v>
-      </c>
-      <c r="G57" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H57" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I57" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J57" s="37" t="s">
+      <c r="B57" s="58">
+        <v>4</v>
+      </c>
+      <c r="C57" s="58">
+        <v>5</v>
+      </c>
+      <c r="D57" s="58">
+        <v>4</v>
+      </c>
+      <c r="E57" s="58">
+        <v>4</v>
+      </c>
+      <c r="F57" s="58">
+        <v>4</v>
+      </c>
+      <c r="G57" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H57" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I57" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J57" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="58" ht="14.5" spans="1:10">
-      <c r="A58" s="44" t="s">
-        <v>63</v>
-      </c>
-      <c r="B58" s="45" t="s">
-        <v>62</v>
-      </c>
-      <c r="C58" s="45" t="s">
-        <v>58</v>
-      </c>
-      <c r="D58" s="45" t="s">
-        <v>61</v>
-      </c>
-      <c r="E58" s="45" t="s">
-        <v>61</v>
-      </c>
-      <c r="F58" s="45" t="s">
-        <v>61</v>
-      </c>
-      <c r="G58" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H58" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I58" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J58" s="37" t="s">
+      <c r="A58" s="57">
+        <v>10</v>
+      </c>
+      <c r="B58" s="58">
+        <v>5</v>
+      </c>
+      <c r="C58" s="58">
+        <v>3</v>
+      </c>
+      <c r="D58" s="58">
+        <v>4</v>
+      </c>
+      <c r="E58" s="58">
+        <v>4</v>
+      </c>
+      <c r="F58" s="58">
+        <v>4</v>
+      </c>
+      <c r="G58" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H58" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I58" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J58" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="59" ht="14.5" spans="1:10">
-      <c r="A59" s="44" t="s">
-        <v>64</v>
-      </c>
-      <c r="B59" s="45" t="s">
-        <v>65</v>
-      </c>
-      <c r="C59" s="45" t="s">
-        <v>61</v>
-      </c>
-      <c r="D59" s="45" t="s">
-        <v>61</v>
-      </c>
-      <c r="E59" s="45" t="s">
-        <v>61</v>
-      </c>
-      <c r="F59" s="45" t="s">
-        <v>61</v>
-      </c>
-      <c r="G59" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H59" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I59" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J59" s="37" t="s">
+      <c r="A59" s="57">
+        <v>9</v>
+      </c>
+      <c r="B59" s="58">
+        <v>6</v>
+      </c>
+      <c r="C59" s="58">
+        <v>4</v>
+      </c>
+      <c r="D59" s="58">
+        <v>4</v>
+      </c>
+      <c r="E59" s="58">
+        <v>4</v>
+      </c>
+      <c r="F59" s="58">
+        <v>4</v>
+      </c>
+      <c r="G59" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H59" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I59" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J59" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="60" ht="14.5" spans="1:10">
-      <c r="A60" s="44" t="s">
+      <c r="A60" s="57" t="s">
         <v>66</v>
       </c>
-      <c r="B60" s="45" t="s">
-        <v>56</v>
-      </c>
-      <c r="C60" s="45" t="s">
-        <v>56</v>
-      </c>
-      <c r="D60" s="45" t="s">
-        <v>56</v>
-      </c>
-      <c r="E60" s="45" t="s">
-        <v>56</v>
-      </c>
-      <c r="F60" s="45" t="s">
-        <v>56</v>
-      </c>
-      <c r="G60" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H60" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I60" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J60" s="37" t="s">
+      <c r="B60" s="58">
+        <v>1</v>
+      </c>
+      <c r="C60" s="58">
+        <v>1</v>
+      </c>
+      <c r="D60" s="58">
+        <v>1</v>
+      </c>
+      <c r="E60" s="58">
+        <v>1</v>
+      </c>
+      <c r="F60" s="58">
+        <v>1</v>
+      </c>
+      <c r="G60" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H60" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I60" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J60" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" ht="14.5" spans="1:10">
-      <c r="A61" s="44" t="s">
+      <c r="A61" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="B61" s="45" t="s">
-        <v>58</v>
-      </c>
-      <c r="C61" s="45" t="s">
-        <v>58</v>
-      </c>
-      <c r="D61" s="45" t="s">
-        <v>58</v>
-      </c>
-      <c r="E61" s="45" t="s">
-        <v>58</v>
-      </c>
-      <c r="F61" s="45" t="s">
-        <v>58</v>
-      </c>
-      <c r="G61" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H61" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I61" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J61" s="37" t="s">
+      <c r="B61" s="58">
+        <v>3</v>
+      </c>
+      <c r="C61" s="58">
+        <v>3</v>
+      </c>
+      <c r="D61" s="58">
+        <v>3</v>
+      </c>
+      <c r="E61" s="58">
+        <v>3</v>
+      </c>
+      <c r="F61" s="58">
+        <v>3</v>
+      </c>
+      <c r="G61" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H61" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I61" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J61" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:10">
-      <c r="A62" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="B62" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C62" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D62" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E62" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F62" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G62" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H62" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I62" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J62" s="37" t="s">
+      <c r="A62" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="B62" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C62" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D62" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E62" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F62" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G62" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H62" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I62" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J62" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="63" ht="16.5" spans="1:10">
-      <c r="A63" s="46" t="s">
+      <c r="A63" s="59" t="s">
         <v>68</v>
       </c>
-      <c r="B63" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C63" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D63" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E63" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F63" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G63" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H63" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I63" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J63" s="37" t="s">
+      <c r="B63" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C63" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D63" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E63" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F63" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G63" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H63" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I63" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J63" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="64" ht="16.5" spans="1:10">
-      <c r="A64" s="41" t="s">
+      <c r="A64" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="B64" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C64" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D64" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E64" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F64" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G64" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H64" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I64" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J64" s="37" t="s">
+      <c r="B64" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C64" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D64" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E64" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F64" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G64" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H64" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I64" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J64" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" ht="60" customHeight="1" spans="1:10">
-      <c r="A65" s="42" t="s">
+      <c r="A65" s="55" t="s">
         <v>70</v>
       </c>
-      <c r="B65" s="42" t="s">
+      <c r="B65" s="55" t="s">
         <v>71</v>
       </c>
-      <c r="C65" s="42" t="s">
+      <c r="C65" s="55" t="s">
         <v>72</v>
       </c>
-      <c r="D65" s="43" t="s">
+      <c r="D65" s="56" t="s">
         <v>73</v>
       </c>
-      <c r="E65" s="43" t="s">
+      <c r="E65" s="56" t="s">
         <v>74</v>
       </c>
-      <c r="F65" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G65" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H65" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I65" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J65" s="37" t="s">
+      <c r="F65" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G65" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H65" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I65" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J65" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="66" ht="45" customHeight="1" spans="1:10">
-      <c r="A66" s="44" t="s">
+      <c r="A66" s="57" t="s">
         <v>75</v>
       </c>
-      <c r="B66" s="45" t="s">
-        <v>63</v>
-      </c>
-      <c r="C66" s="44" t="s">
+      <c r="B66" s="58">
+        <v>10</v>
+      </c>
+      <c r="C66" s="57" t="s">
         <v>76</v>
       </c>
-      <c r="D66" s="45" t="s">
-        <v>77</v>
-      </c>
-      <c r="E66" s="45" t="s">
-        <v>78</v>
-      </c>
-      <c r="F66" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G66" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H66" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I66" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J66" s="37" t="s">
+      <c r="D66" s="62">
+        <v>0.0024</v>
+      </c>
+      <c r="E66" s="63">
+        <v>0.024384</v>
+      </c>
+      <c r="F66" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G66" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H66" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I66" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J66" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="67" ht="29" spans="1:10">
-      <c r="A67" s="44" t="s">
+      <c r="A67" s="57" t="s">
         <v>79</v>
       </c>
-      <c r="B67" s="45" t="s">
-        <v>62</v>
-      </c>
-      <c r="C67" s="44" t="s">
+      <c r="B67" s="58">
+        <v>5</v>
+      </c>
+      <c r="C67" s="57" t="s">
         <v>80</v>
       </c>
-      <c r="D67" s="45" t="s">
-        <v>81</v>
-      </c>
-      <c r="E67" s="45" t="s">
-        <v>82</v>
-      </c>
-      <c r="F67" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G67" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H67" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I67" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J67" s="37" t="s">
+      <c r="D67" s="62">
+        <v>0.0004</v>
+      </c>
+      <c r="E67" s="63">
+        <v>0.002152</v>
+      </c>
+      <c r="F67" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G67" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H67" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I67" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J67" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="68" ht="14.5" spans="1:10">
-      <c r="A68" s="44" t="s">
+      <c r="A68" s="57" t="s">
         <v>83</v>
       </c>
-      <c r="B68" s="45" t="s">
-        <v>56</v>
-      </c>
-      <c r="C68" s="45" t="s">
+      <c r="B68" s="58">
+        <v>1</v>
+      </c>
+      <c r="C68" s="58" t="s">
         <v>84</v>
       </c>
-      <c r="D68" s="45" t="s">
-        <v>85</v>
-      </c>
-      <c r="E68" s="45" t="s">
-        <v>86</v>
-      </c>
-      <c r="F68" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G68" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H68" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I68" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J68" s="37" t="s">
+      <c r="D68" s="62">
+        <v>0.0001</v>
+      </c>
+      <c r="E68" s="63">
+        <v>0.000076</v>
+      </c>
+      <c r="F68" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G68" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H68" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I68" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J68" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:10">
-      <c r="A69" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="B69" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C69" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D69" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E69" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F69" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G69" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H69" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I69" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J69" s="37" t="s">
+      <c r="A69" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="B69" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C69" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D69" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E69" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F69" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G69" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H69" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I69" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J69" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="70" ht="16.5" spans="1:10">
-      <c r="A70" s="47" t="s">
+      <c r="A70" s="60" t="s">
         <v>87</v>
       </c>
-      <c r="B70" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C70" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D70" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E70" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F70" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G70" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H70" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I70" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J70" s="37" t="s">
+      <c r="B70" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C70" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D70" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E70" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F70" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G70" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H70" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I70" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J70" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1" spans="1:10">
-      <c r="A71" s="40" t="s">
+      <c r="A71" s="53" t="s">
         <v>88</v>
       </c>
-      <c r="B71" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C71" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D71" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E71" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F71" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G71" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H71" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I71" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J71" s="37" t="s">
+      <c r="B71" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C71" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D71" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E71" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F71" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G71" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H71" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I71" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J71" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:10">
-      <c r="A72" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="B72" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C72" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D72" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E72" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F72" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G72" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H72" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I72" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J72" s="37" t="s">
+      <c r="A72" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="B72" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C72" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D72" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E72" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F72" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G72" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H72" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I72" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J72" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" ht="16.5" spans="1:10">
-      <c r="A73" s="46" t="s">
+      <c r="A73" s="59" t="s">
         <v>89</v>
       </c>
-      <c r="B73" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C73" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D73" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E73" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F73" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G73" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H73" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I73" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J73" s="37" t="s">
+      <c r="B73" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C73" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D73" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E73" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F73" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G73" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H73" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I73" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J73" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="74" ht="16.5" spans="1:10">
-      <c r="A74" s="41" t="s">
+      <c r="A74" s="54" t="s">
         <v>90</v>
       </c>
-      <c r="B74" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C74" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D74" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E74" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F74" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G74" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H74" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I74" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J74" s="37" t="s">
+      <c r="B74" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C74" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D74" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E74" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F74" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G74" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H74" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I74" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J74" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="75" ht="16.5" spans="1:10">
-      <c r="A75" s="46" t="s">
+      <c r="A75" s="59" t="s">
         <v>91</v>
       </c>
-      <c r="B75" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C75" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D75" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E75" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F75" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G75" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H75" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I75" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J75" s="37" t="s">
+      <c r="B75" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C75" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D75" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E75" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F75" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G75" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H75" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I75" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J75" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="76" ht="16.5" spans="1:10">
-      <c r="A76" s="41" t="s">
+      <c r="A76" s="54" t="s">
         <v>92</v>
       </c>
-      <c r="B76" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C76" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D76" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E76" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F76" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G76" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H76" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I76" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J76" s="37" t="s">
+      <c r="B76" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C76" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D76" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E76" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F76" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G76" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H76" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I76" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J76" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" ht="16.5" spans="1:10">
-      <c r="A77" s="41" t="s">
+      <c r="A77" s="54" t="s">
         <v>93</v>
       </c>
-      <c r="B77" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C77" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D77" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E77" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F77" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G77" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H77" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I77" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J77" s="37" t="s">
+      <c r="B77" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C77" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D77" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E77" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F77" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G77" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H77" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I77" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J77" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1" spans="1:10">
-      <c r="A78" s="42" t="s">
+      <c r="A78" s="55" t="s">
         <v>70</v>
       </c>
-      <c r="B78" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="C78" s="43" t="s">
-        <v>61</v>
-      </c>
-      <c r="D78" s="43" t="s">
-        <v>62</v>
-      </c>
-      <c r="E78" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F78" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G78" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H78" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I78" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J78" s="37" t="s">
+      <c r="B78" s="56">
+        <v>3</v>
+      </c>
+      <c r="C78" s="56">
+        <v>4</v>
+      </c>
+      <c r="D78" s="56">
+        <v>5</v>
+      </c>
+      <c r="E78" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F78" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G78" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H78" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I78" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J78" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="79" ht="14.5" spans="1:10">
-      <c r="A79" s="44" t="s">
+      <c r="A79" s="57" t="s">
         <v>94</v>
       </c>
-      <c r="B79" s="45" t="s">
-        <v>63</v>
-      </c>
-      <c r="C79" s="45" t="s">
-        <v>95</v>
-      </c>
-      <c r="D79" s="45" t="s">
-        <v>53</v>
-      </c>
-      <c r="E79" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F79" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G79" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H79" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I79" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J79" s="37" t="s">
+      <c r="B79" s="58">
+        <v>10</v>
+      </c>
+      <c r="C79" s="58">
+        <v>15</v>
+      </c>
+      <c r="D79" s="58">
+        <v>20</v>
+      </c>
+      <c r="E79" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F79" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G79" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H79" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I79" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J79" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="80" ht="14.5" spans="1:10">
-      <c r="A80" s="44" t="s">
+      <c r="A80" s="57" t="s">
         <v>96</v>
       </c>
-      <c r="B80" s="45" t="s">
-        <v>78</v>
-      </c>
-      <c r="C80" s="45" t="s">
-        <v>82</v>
-      </c>
-      <c r="D80" s="45" t="s">
-        <v>86</v>
-      </c>
-      <c r="E80" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F80" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G80" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H80" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I80" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J80" s="37" t="s">
+      <c r="B80" s="63">
+        <v>0.024384</v>
+      </c>
+      <c r="C80" s="63">
+        <v>0.002152</v>
+      </c>
+      <c r="D80" s="63">
+        <v>0.000076</v>
+      </c>
+      <c r="E80" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F80" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G80" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H80" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I80" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J80" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" ht="14.5" spans="1:10">
-      <c r="A81" s="44" t="s">
+      <c r="A81" s="57" t="s">
         <v>97</v>
       </c>
-      <c r="B81" s="45" t="s">
-        <v>98</v>
-      </c>
-      <c r="C81" s="45" t="s">
-        <v>99</v>
-      </c>
-      <c r="D81" s="45" t="s">
-        <v>100</v>
-      </c>
-      <c r="E81" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F81" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G81" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H81" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I81" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J81" s="37" t="s">
+      <c r="B81" s="63">
+        <v>0.025064</v>
+      </c>
+      <c r="C81" s="63">
+        <v>0.002238</v>
+      </c>
+      <c r="D81" s="63">
+        <v>0.00008</v>
+      </c>
+      <c r="E81" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F81" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G81" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H81" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I81" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J81" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="82" ht="14.5" spans="1:10">
-      <c r="A82" s="44" t="s">
+      <c r="A82" s="57" t="s">
         <v>101</v>
       </c>
-      <c r="B82" s="45" t="s">
-        <v>102</v>
-      </c>
-      <c r="C82" s="45" t="s">
-        <v>103</v>
-      </c>
-      <c r="D82" s="45" t="s">
-        <v>104</v>
-      </c>
-      <c r="E82" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F82" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G82" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H82" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I82" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J82" s="37" t="s">
+      <c r="B82" s="58">
+        <v>14.0019</v>
+      </c>
+      <c r="C82" s="58">
+        <v>21.0028</v>
+      </c>
+      <c r="D82" s="58">
+        <v>28.0037</v>
+      </c>
+      <c r="E82" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F82" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G82" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H82" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I82" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J82" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="83" ht="14.5" spans="1:10">
-      <c r="A83" s="44" t="s">
+      <c r="A83" s="57" t="s">
         <v>105</v>
       </c>
-      <c r="B83" s="45" t="s">
-        <v>106</v>
-      </c>
-      <c r="C83" s="45" t="s">
-        <v>107</v>
-      </c>
-      <c r="D83" s="45" t="s">
-        <v>108</v>
-      </c>
-      <c r="E83" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F83" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G83" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H83" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I83" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J83" s="37" t="s">
+      <c r="B83" s="62">
+        <v>0.3492</v>
+      </c>
+      <c r="C83" s="62">
+        <v>0.0462</v>
+      </c>
+      <c r="D83" s="62">
+        <v>0.0022</v>
+      </c>
+      <c r="E83" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F83" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G83" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H83" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I83" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J83" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:10">
-      <c r="A84" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="B84" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C84" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D84" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E84" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F84" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G84" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H84" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I84" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J84" s="37" t="s">
+      <c r="A84" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="B84" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C84" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D84" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E84" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F84" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G84" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H84" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I84" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J84" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" ht="16.5" spans="1:10">
-      <c r="A85" s="41" t="s">
+      <c r="A85" s="54" t="s">
         <v>109</v>
       </c>
-      <c r="B85" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C85" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D85" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E85" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F85" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G85" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H85" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I85" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J85" s="37" t="s">
+      <c r="B85" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C85" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D85" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E85" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F85" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G85" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H85" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I85" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J85" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1" spans="1:10">
-      <c r="A86" s="40" t="s">
+      <c r="A86" s="53" t="s">
         <v>110</v>
       </c>
-      <c r="B86" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C86" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D86" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E86" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F86" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G86" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H86" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I86" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J86" s="37" t="s">
+      <c r="B86" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C86" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D86" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E86" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F86" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G86" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H86" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I86" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J86" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:10">
-      <c r="A87" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="B87" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C87" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D87" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E87" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F87" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G87" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H87" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I87" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J87" s="37" t="s">
+      <c r="A87" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="B87" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C87" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D87" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E87" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F87" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G87" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H87" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I87" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J87" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="88" ht="17" customHeight="1" spans="1:10">
-      <c r="A88" s="48" t="s">
+      <c r="A88" s="61" t="s">
         <v>111</v>
       </c>
-      <c r="B88" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C88" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D88" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E88" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F88" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G88" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H88" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I88" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J88" s="37" t="s">
+      <c r="B88" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C88" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D88" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E88" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F88" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G88" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H88" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I88" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J88" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" ht="16.5" spans="1:10">
-      <c r="A89" s="41" t="s">
+      <c r="A89" s="54" t="s">
         <v>112</v>
       </c>
-      <c r="B89" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C89" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D89" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E89" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F89" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G89" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H89" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I89" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J89" s="37" t="s">
+      <c r="B89" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C89" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D89" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E89" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F89" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G89" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H89" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I89" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J89" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="90" ht="16.5" spans="1:10">
-      <c r="A90" s="41" t="s">
+      <c r="A90" s="54" t="s">
         <v>113</v>
       </c>
-      <c r="B90" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C90" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D90" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E90" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F90" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G90" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H90" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I90" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J90" s="37" t="s">
+      <c r="B90" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C90" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D90" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E90" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F90" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G90" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H90" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I90" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J90" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="91" ht="16.5" spans="1:10">
-      <c r="A91" s="41" t="s">
+      <c r="A91" s="54" t="s">
         <v>114</v>
       </c>
-      <c r="B91" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C91" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D91" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E91" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F91" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G91" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H91" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I91" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J91" s="37" t="s">
+      <c r="B91" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C91" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D91" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E91" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F91" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G91" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H91" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I91" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J91" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="92" ht="17" customHeight="1" spans="1:10">
-      <c r="A92" s="48" t="s">
+      <c r="A92" s="61" t="s">
         <v>115</v>
       </c>
-      <c r="B92" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C92" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D92" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E92" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F92" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G92" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H92" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I92" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J92" s="37" t="s">
+      <c r="B92" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C92" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D92" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E92" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F92" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G92" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H92" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I92" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J92" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" ht="16.5" spans="1:10">
-      <c r="A93" s="46" t="s">
+      <c r="A93" s="59" t="s">
         <v>116</v>
       </c>
-      <c r="B93" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C93" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D93" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E93" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F93" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G93" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H93" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I93" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J93" s="37" t="s">
+      <c r="B93" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C93" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D93" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E93" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F93" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G93" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H93" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I93" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J93" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="94" ht="16.5" spans="1:10">
-      <c r="A94" s="41" t="s">
+      <c r="A94" s="54" t="s">
         <v>117</v>
       </c>
-      <c r="B94" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C94" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D94" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E94" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F94" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G94" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H94" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I94" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J94" s="37" t="s">
+      <c r="B94" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C94" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D94" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E94" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F94" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G94" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H94" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I94" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J94" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="95" ht="16.5" spans="1:10">
-      <c r="A95" s="46" t="s">
+      <c r="A95" s="59" t="s">
         <v>118</v>
       </c>
-      <c r="B95" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C95" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D95" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E95" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F95" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G95" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H95" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I95" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J95" s="37" t="s">
+      <c r="B95" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C95" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D95" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E95" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F95" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G95" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H95" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I95" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J95" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="96" ht="16.5" spans="1:10">
-      <c r="A96" s="41" t="s">
+      <c r="A96" s="54" t="s">
         <v>119</v>
       </c>
-      <c r="B96" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C96" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D96" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E96" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F96" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G96" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H96" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I96" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J96" s="37" t="s">
+      <c r="B96" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C96" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D96" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E96" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F96" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G96" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H96" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I96" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J96" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" ht="16.5" spans="1:10">
-      <c r="A97" s="41" t="s">
+      <c r="A97" s="54" t="s">
         <v>120</v>
       </c>
-      <c r="B97" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C97" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D97" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E97" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F97" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G97" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H97" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I97" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J97" s="37" t="s">
+      <c r="B97" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C97" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D97" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E97" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F97" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G97" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H97" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I97" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J97" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="98" ht="17" customHeight="1" spans="1:10">
-      <c r="A98" s="48" t="s">
+      <c r="A98" s="61" t="s">
         <v>121</v>
       </c>
-      <c r="B98" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C98" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D98" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E98" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F98" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G98" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H98" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I98" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J98" s="37" t="s">
+      <c r="B98" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C98" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D98" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E98" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F98" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G98" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H98" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I98" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J98" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="99" ht="16.5" spans="1:10">
-      <c r="A99" s="41" t="s">
+      <c r="A99" s="54" t="s">
         <v>122</v>
       </c>
-      <c r="B99" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C99" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D99" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E99" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F99" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G99" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H99" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I99" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J99" s="37" t="s">
+      <c r="B99" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C99" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D99" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E99" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F99" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G99" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H99" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I99" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J99" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="100" ht="16.5" spans="1:10">
-      <c r="A100" s="46" t="s">
+      <c r="A100" s="59" t="s">
         <v>123</v>
       </c>
-      <c r="B100" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C100" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D100" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E100" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F100" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G100" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H100" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I100" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J100" s="37" t="s">
+      <c r="B100" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C100" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D100" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E100" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F100" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G100" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H100" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I100" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J100" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" ht="16.5" spans="1:10">
-      <c r="A101" s="41" t="s">
+      <c r="A101" s="54" t="s">
         <v>124</v>
       </c>
-      <c r="B101" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C101" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D101" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E101" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F101" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G101" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H101" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I101" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J101" s="37" t="s">
+      <c r="B101" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C101" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D101" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E101" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F101" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G101" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H101" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I101" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J101" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="102" ht="16.5" spans="1:10">
-      <c r="A102" s="41" t="s">
+      <c r="A102" s="54" t="s">
         <v>125</v>
       </c>
-      <c r="B102" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C102" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D102" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E102" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F102" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G102" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H102" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I102" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J102" s="37" t="s">
+      <c r="B102" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C102" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D102" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E102" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F102" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G102" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H102" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I102" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J102" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="103" ht="16.5" spans="1:10">
-      <c r="A103" s="41" t="s">
+      <c r="A103" s="54" t="s">
         <v>126</v>
       </c>
-      <c r="B103" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C103" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D103" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E103" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F103" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G103" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H103" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I103" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J103" s="37" t="s">
+      <c r="B103" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C103" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D103" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E103" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F103" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G103" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H103" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I103" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J103" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="104" ht="16.5" spans="1:10">
-      <c r="A104" s="47" t="s">
+      <c r="A104" s="60" t="s">
         <v>127</v>
       </c>
-      <c r="B104" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C104" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D104" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E104" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F104" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G104" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H104" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I104" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J104" s="37" t="s">
+      <c r="B104" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C104" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D104" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E104" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F104" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G104" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H104" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I104" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J104" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="105" ht="20" customHeight="1" spans="1:10">
-      <c r="A105" s="40" t="s">
+      <c r="A105" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="B105" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C105" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D105" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E105" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F105" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G105" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H105" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I105" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J105" s="37" t="s">
+      <c r="B105" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C105" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D105" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E105" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F105" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G105" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H105" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I105" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J105" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="106" spans="1:10">
-      <c r="A106" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="B106" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C106" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D106" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E106" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F106" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G106" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H106" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I106" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J106" s="37" t="s">
+      <c r="A106" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="B106" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C106" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D106" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E106" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F106" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G106" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H106" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I106" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J106" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="107" ht="16.5" spans="1:10">
-      <c r="A107" s="41" t="s">
+      <c r="A107" s="54" t="s">
         <v>129</v>
       </c>
-      <c r="B107" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C107" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D107" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E107" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F107" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G107" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H107" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I107" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J107" s="37" t="s">
+      <c r="B107" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C107" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D107" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E107" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F107" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G107" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H107" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I107" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J107" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="108" ht="16.5" spans="1:10">
-      <c r="A108" s="41" t="s">
+      <c r="A108" s="54" t="s">
         <v>130</v>
       </c>
-      <c r="B108" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C108" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D108" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E108" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F108" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G108" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H108" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I108" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J108" s="37" t="s">
+      <c r="B108" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C108" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D108" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E108" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F108" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G108" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H108" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I108" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J108" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="109" ht="16.5" spans="1:10">
-      <c r="A109" s="41" t="s">
+      <c r="A109" s="54" t="s">
         <v>131</v>
       </c>
-      <c r="B109" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C109" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D109" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E109" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F109" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G109" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H109" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I109" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J109" s="37" t="s">
+      <c r="B109" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C109" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D109" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E109" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F109" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G109" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H109" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I109" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J109" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="110" ht="16.5" spans="1:10">
-      <c r="A110" s="41" t="s">
+      <c r="A110" s="54" t="s">
         <v>132</v>
       </c>
-      <c r="B110" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C110" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D110" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E110" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F110" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G110" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H110" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I110" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J110" s="37" t="s">
+      <c r="B110" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C110" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D110" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E110" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F110" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G110" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H110" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I110" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J110" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="111" ht="16.5" spans="1:10">
-      <c r="A111" s="41" t="s">
+      <c r="A111" s="54" t="s">
         <v>133</v>
       </c>
-      <c r="B111" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C111" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D111" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E111" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F111" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G111" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H111" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I111" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J111" s="37" t="s">
+      <c r="B111" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C111" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D111" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E111" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F111" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G111" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H111" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I111" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J111" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="112" ht="16.5" spans="1:10">
-      <c r="A112" s="41" t="s">
+      <c r="A112" s="54" t="s">
         <v>134</v>
       </c>
-      <c r="B112" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C112" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D112" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E112" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F112" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G112" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H112" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I112" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J112" s="37" t="s">
+      <c r="B112" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C112" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D112" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E112" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F112" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G112" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H112" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I112" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J112" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="113" ht="16.5" spans="1:10">
-      <c r="A113" s="39" t="s">
+      <c r="A113" s="52" t="s">
         <v>135</v>
       </c>
-      <c r="B113" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C113" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D113" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E113" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F113" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G113" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H113" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I113" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J113" s="37" t="s">
+      <c r="B113" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C113" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D113" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E113" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F113" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G113" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H113" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I113" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J113" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="114" ht="20" customHeight="1" spans="1:10">
-      <c r="A114" s="40" t="s">
+      <c r="A114" s="53" t="s">
         <v>136</v>
       </c>
-      <c r="B114" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C114" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D114" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E114" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F114" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G114" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H114" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I114" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J114" s="37" t="s">
+      <c r="B114" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C114" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D114" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E114" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F114" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G114" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H114" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I114" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J114" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="115" spans="1:10">
-      <c r="A115" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="B115" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C115" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D115" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E115" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F115" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G115" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H115" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I115" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J115" s="37" t="s">
+      <c r="A115" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="B115" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C115" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D115" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E115" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F115" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G115" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H115" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I115" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J115" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1" spans="1:10">
-      <c r="A116" s="42" t="s">
+      <c r="A116" s="55" t="s">
         <v>137</v>
       </c>
-      <c r="B116" s="43" t="s">
+      <c r="B116" s="56" t="s">
         <v>138</v>
       </c>
-      <c r="C116" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D116" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E116" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F116" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G116" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H116" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I116" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J116" s="37" t="s">
+      <c r="C116" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D116" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E116" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F116" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G116" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H116" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I116" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J116" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="117" ht="14.5" spans="1:10">
-      <c r="A117" s="44" t="s">
+      <c r="A117" s="57" t="s">
         <v>139</v>
       </c>
-      <c r="B117" s="45" t="s">
+      <c r="B117" s="58" t="s">
         <v>140</v>
       </c>
-      <c r="C117" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D117" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E117" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F117" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G117" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H117" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I117" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J117" s="37" t="s">
+      <c r="C117" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D117" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E117" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F117" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G117" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H117" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I117" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J117" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="118" ht="14.5" spans="1:10">
-      <c r="A118" s="44" t="s">
+      <c r="A118" s="57" t="s">
         <v>141</v>
       </c>
-      <c r="B118" s="45" t="s">
+      <c r="B118" s="58" t="s">
         <v>142</v>
       </c>
-      <c r="C118" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D118" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E118" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F118" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G118" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H118" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I118" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J118" s="37" t="s">
+      <c r="C118" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D118" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E118" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F118" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G118" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H118" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I118" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J118" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="119" ht="14.5" spans="1:10">
-      <c r="A119" s="44" t="s">
+      <c r="A119" s="57" t="s">
         <v>143</v>
       </c>
-      <c r="B119" s="45" t="s">
+      <c r="B119" s="58" t="s">
         <v>144</v>
       </c>
-      <c r="C119" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D119" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E119" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F119" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G119" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H119" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I119" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J119" s="37" t="s">
+      <c r="C119" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D119" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E119" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F119" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G119" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H119" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I119" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J119" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="120" ht="14.5" spans="1:10">
-      <c r="A120" s="44" t="s">
+      <c r="A120" s="57" t="s">
         <v>145</v>
       </c>
-      <c r="B120" s="45" t="s">
+      <c r="B120" s="58" t="s">
         <v>146</v>
       </c>
-      <c r="C120" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D120" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E120" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F120" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G120" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H120" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I120" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J120" s="37" t="s">
+      <c r="C120" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D120" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E120" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F120" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G120" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H120" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I120" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J120" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="121" ht="14.5" spans="1:10">
-      <c r="A121" s="44" t="s">
+      <c r="A121" s="57" t="s">
         <v>101</v>
       </c>
-      <c r="B121" s="45" t="s">
+      <c r="B121" s="58" t="s">
         <v>147</v>
       </c>
-      <c r="C121" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D121" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E121" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F121" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G121" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H121" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I121" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J121" s="37" t="s">
+      <c r="C121" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D121" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E121" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F121" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G121" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H121" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I121" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J121" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="122" ht="14.5" spans="1:10">
-      <c r="A122" s="44" t="s">
+      <c r="A122" s="57" t="s">
         <v>148</v>
       </c>
-      <c r="B122" s="45" t="s">
+      <c r="B122" s="58" t="s">
         <v>149</v>
       </c>
-      <c r="C122" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D122" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E122" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F122" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G122" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H122" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I122" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J122" s="37" t="s">
+      <c r="C122" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D122" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E122" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F122" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G122" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H122" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I122" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J122" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="123" ht="14.5" spans="1:10">
-      <c r="A123" s="44" t="s">
+      <c r="A123" s="57" t="s">
         <v>150</v>
       </c>
-      <c r="B123" s="45" t="s">
+      <c r="B123" s="58" t="s">
         <v>151</v>
       </c>
-      <c r="C123" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D123" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E123" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F123" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G123" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H123" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I123" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J123" s="37" t="s">
+      <c r="C123" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D123" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E123" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F123" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G123" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H123" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I123" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J123" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:10">
-      <c r="A124" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="B124" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C124" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D124" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E124" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F124" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G124" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H124" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I124" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J124" s="37" t="s">
+      <c r="A124" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="B124" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C124" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D124" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E124" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F124" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G124" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H124" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I124" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J124" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="125" ht="16.5" spans="1:10">
-      <c r="A125" s="46" t="s">
+      <c r="A125" s="59" t="s">
         <v>152</v>
       </c>
-      <c r="B125" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C125" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D125" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E125" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F125" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G125" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H125" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I125" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J125" s="37" t="s">
+      <c r="B125" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C125" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D125" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E125" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F125" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G125" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H125" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I125" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J125" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="126" ht="20" customHeight="1" spans="1:10">
-      <c r="A126" s="40" t="s">
+      <c r="A126" s="53" t="s">
         <v>153</v>
       </c>
-      <c r="B126" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C126" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D126" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E126" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F126" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G126" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H126" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I126" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J126" s="37" t="s">
+      <c r="B126" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C126" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D126" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E126" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F126" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G126" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H126" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I126" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J126" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:10">
-      <c r="A127" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="B127" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C127" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D127" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E127" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F127" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G127" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H127" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I127" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J127" s="37" t="s">
+      <c r="A127" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="B127" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C127" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D127" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E127" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F127" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G127" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H127" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I127" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J127" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="128" ht="16.5" spans="1:10">
-      <c r="A128" s="46" t="s">
+      <c r="A128" s="59" t="s">
         <v>154</v>
       </c>
-      <c r="B128" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C128" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D128" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E128" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F128" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G128" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H128" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I128" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J128" s="37" t="s">
+      <c r="B128" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C128" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D128" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E128" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F128" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G128" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H128" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I128" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J128" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="129" ht="16.5" spans="1:10">
-      <c r="A129" s="41" t="s">
+      <c r="A129" s="54" t="s">
         <v>155</v>
       </c>
-      <c r="B129" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C129" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D129" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E129" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F129" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G129" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H129" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I129" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J129" s="37" t="s">
+      <c r="B129" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C129" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D129" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E129" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F129" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G129" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H129" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I129" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J129" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="130" ht="16.5" spans="1:10">
-      <c r="A130" s="41" t="s">
+      <c r="A130" s="54" t="s">
         <v>156</v>
       </c>
-      <c r="B130" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C130" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D130" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E130" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F130" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G130" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H130" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I130" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J130" s="37" t="s">
+      <c r="B130" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C130" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D130" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E130" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F130" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G130" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H130" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I130" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J130" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="131" ht="16.5" spans="1:10">
-      <c r="A131" s="41" t="s">
+      <c r="A131" s="54" t="s">
         <v>157</v>
       </c>
-      <c r="B131" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C131" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D131" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E131" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F131" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G131" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H131" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I131" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J131" s="37" t="s">
+      <c r="B131" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C131" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D131" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E131" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F131" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G131" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H131" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I131" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J131" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="132" ht="16.5" spans="1:10">
-      <c r="A132" s="41" t="s">
+      <c r="A132" s="54" t="s">
         <v>158</v>
       </c>
-      <c r="B132" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C132" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D132" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E132" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F132" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G132" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H132" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I132" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J132" s="37" t="s">
+      <c r="B132" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C132" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D132" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E132" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F132" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G132" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H132" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I132" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J132" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="133" ht="20" customHeight="1" spans="1:10">
-      <c r="A133" s="40" t="s">
+      <c r="A133" s="53" t="s">
         <v>159</v>
       </c>
-      <c r="B133" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C133" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D133" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E133" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F133" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G133" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H133" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I133" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J133" s="37" t="s">
+      <c r="B133" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C133" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D133" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E133" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F133" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G133" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H133" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I133" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J133" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="134" spans="1:10">
-      <c r="A134" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="B134" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C134" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D134" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E134" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F134" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G134" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H134" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I134" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J134" s="37" t="s">
+      <c r="A134" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="B134" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C134" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D134" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E134" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F134" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G134" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H134" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I134" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J134" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="135" ht="18" customHeight="1" spans="1:10">
-      <c r="A135" s="42" t="s">
+      <c r="A135" s="55" t="s">
         <v>160</v>
       </c>
-      <c r="B135" s="43" t="s">
+      <c r="B135" s="56" t="s">
         <v>161</v>
       </c>
-      <c r="C135" s="43" t="s">
+      <c r="C135" s="56" t="s">
         <v>162</v>
       </c>
-      <c r="D135" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E135" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F135" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G135" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H135" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I135" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J135" s="37" t="s">
+      <c r="D135" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E135" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F135" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G135" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H135" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I135" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J135" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="136" ht="14.5" spans="1:10">
-      <c r="A136" s="44" t="s">
+      <c r="A136" s="57" t="s">
         <v>163</v>
       </c>
-      <c r="B136" s="45" t="s">
+      <c r="B136" s="58" t="s">
         <v>164</v>
       </c>
-      <c r="C136" s="45" t="s">
+      <c r="C136" s="58" t="s">
         <v>165</v>
       </c>
-      <c r="D136" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E136" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F136" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G136" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H136" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I136" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J136" s="37" t="s">
+      <c r="D136" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E136" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F136" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G136" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H136" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I136" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J136" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="137" ht="14.5" spans="1:10">
-      <c r="A137" s="44" t="s">
+      <c r="A137" s="57" t="s">
         <v>166</v>
       </c>
-      <c r="B137" s="45" t="s">
+      <c r="B137" s="58" t="s">
         <v>167</v>
       </c>
-      <c r="C137" s="45" t="s">
+      <c r="C137" s="58" t="s">
         <v>168</v>
       </c>
-      <c r="D137" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E137" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F137" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G137" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H137" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I137" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J137" s="37" t="s">
+      <c r="D137" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E137" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F137" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G137" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H137" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I137" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J137" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="138" ht="14.5" spans="1:10">
-      <c r="A138" s="44" t="s">
+      <c r="A138" s="57" t="s">
         <v>169</v>
       </c>
-      <c r="B138" s="45" t="s">
+      <c r="B138" s="58" t="s">
         <v>170</v>
       </c>
-      <c r="C138" s="45" t="s">
+      <c r="C138" s="58" t="s">
         <v>171</v>
       </c>
-      <c r="D138" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E138" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F138" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G138" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H138" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I138" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J138" s="37" t="s">
+      <c r="D138" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E138" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F138" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G138" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H138" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I138" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J138" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="139" ht="14.5" spans="1:10">
-      <c r="A139" s="44" t="s">
+      <c r="A139" s="57" t="s">
         <v>172</v>
       </c>
-      <c r="B139" s="45" t="s">
+      <c r="B139" s="58" t="s">
         <v>173</v>
       </c>
-      <c r="C139" s="45" t="s">
+      <c r="C139" s="58" t="s">
         <v>174</v>
       </c>
-      <c r="D139" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E139" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F139" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G139" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H139" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I139" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J139" s="37" t="s">
+      <c r="D139" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E139" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F139" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G139" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H139" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I139" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J139" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="140" ht="14.5" spans="1:10">
-      <c r="A140" s="44" t="s">
+      <c r="A140" s="57" t="s">
         <v>175</v>
       </c>
-      <c r="B140" s="45" t="s">
+      <c r="B140" s="58" t="s">
         <v>176</v>
       </c>
-      <c r="C140" s="45" t="s">
+      <c r="C140" s="58" t="s">
         <v>177</v>
       </c>
-      <c r="D140" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E140" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F140" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G140" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H140" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I140" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J140" s="37" t="s">
+      <c r="D140" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E140" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F140" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G140" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H140" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I140" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J140" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="141" spans="1:10">
-      <c r="A141" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="B141" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C141" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D141" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E141" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F141" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G141" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H141" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I141" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J141" s="37" t="s">
+      <c r="A141" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="B141" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C141" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D141" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E141" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F141" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G141" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H141" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I141" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J141" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="142" ht="20" customHeight="1" spans="1:10">
-      <c r="A142" s="40" t="s">
+      <c r="A142" s="53" t="s">
         <v>178</v>
       </c>
-      <c r="B142" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C142" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D142" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E142" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F142" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G142" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H142" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I142" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J142" s="37" t="s">
+      <c r="B142" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C142" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D142" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E142" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F142" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G142" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H142" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I142" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J142" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="143" spans="1:10">
-      <c r="A143" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="B143" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C143" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D143" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E143" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F143" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G143" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H143" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I143" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J143" s="37" t="s">
+      <c r="A143" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="B143" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C143" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D143" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E143" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F143" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G143" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H143" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I143" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J143" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="144" ht="16.5" spans="1:10">
-      <c r="A144" s="41" t="s">
+      <c r="A144" s="54" t="s">
         <v>179</v>
       </c>
-      <c r="B144" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C144" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D144" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E144" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F144" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G144" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H144" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I144" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J144" s="37" t="s">
+      <c r="B144" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C144" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D144" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E144" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F144" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G144" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H144" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I144" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J144" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="145" ht="16.5" spans="1:10">
-      <c r="A145" s="41" t="s">
+      <c r="A145" s="54" t="s">
         <v>180</v>
       </c>
-      <c r="B145" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C145" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D145" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E145" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F145" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G145" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H145" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I145" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J145" s="37" t="s">
+      <c r="B145" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C145" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D145" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E145" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F145" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G145" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H145" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I145" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J145" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="146" ht="16.5" spans="1:10">
-      <c r="A146" s="41" t="s">
+      <c r="A146" s="54" t="s">
         <v>181</v>
       </c>
-      <c r="B146" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C146" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D146" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E146" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F146" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G146" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H146" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I146" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J146" s="37" t="s">
+      <c r="B146" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C146" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D146" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E146" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F146" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G146" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H146" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I146" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J146" s="50" t="s">
         <v>1</v>
       </c>
     </row>
@@ -7355,8 +7392,8 @@
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:11">
-      <c r="A7" s="7" t="s">
-        <v>63</v>
+      <c r="A7" s="64">
+        <v>10</v>
       </c>
       <c r="B7" s="7">
         <v>5</v>
@@ -7390,8 +7427,8 @@
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:11">
-      <c r="A8" s="7" t="s">
-        <v>64</v>
+      <c r="A8" s="64">
+        <v>9</v>
       </c>
       <c r="B8" s="7">
         <v>5</v>
@@ -7990,8 +8027,8 @@
       <c r="A25" s="11">
         <v>9</v>
       </c>
-      <c r="B25" s="12" t="s">
-        <v>63</v>
+      <c r="B25" s="65">
+        <v>10</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>60</v>
@@ -8025,8 +8062,8 @@
       <c r="A26" s="11">
         <v>10</v>
       </c>
-      <c r="B26" s="12" t="s">
-        <v>63</v>
+      <c r="B26" s="65">
+        <v>10</v>
       </c>
       <c r="C26" s="12" t="s">
         <v>60</v>
@@ -8060,8 +8097,8 @@
       <c r="A27" s="11">
         <v>11</v>
       </c>
-      <c r="B27" s="12" t="s">
-        <v>63</v>
+      <c r="B27" s="65">
+        <v>10</v>
       </c>
       <c r="C27" s="12" t="s">
         <v>60</v>
@@ -8095,20 +8132,20 @@
       <c r="A28" s="11">
         <v>12</v>
       </c>
-      <c r="B28" s="12" t="s">
-        <v>63</v>
+      <c r="B28" s="65">
+        <v>10</v>
       </c>
       <c r="C28" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="D28" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="E28" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="F28" s="12" t="s">
-        <v>63</v>
+      <c r="D28" s="65">
+        <v>10</v>
+      </c>
+      <c r="E28" s="65">
+        <v>10</v>
+      </c>
+      <c r="F28" s="65">
+        <v>10</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>1</v>
@@ -8130,20 +8167,20 @@
       <c r="A29" s="11">
         <v>13</v>
       </c>
-      <c r="B29" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="E29" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="F29" s="12" t="s">
-        <v>63</v>
+      <c r="B29" s="65">
+        <v>10</v>
+      </c>
+      <c r="C29" s="65">
+        <v>10</v>
+      </c>
+      <c r="D29" s="65">
+        <v>10</v>
+      </c>
+      <c r="E29" s="65">
+        <v>10</v>
+      </c>
+      <c r="F29" s="65">
+        <v>10</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>1</v>
@@ -8165,20 +8202,20 @@
       <c r="A30" s="11">
         <v>14</v>
       </c>
-      <c r="B30" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="D30" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="E30" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="F30" s="12" t="s">
-        <v>63</v>
+      <c r="B30" s="65">
+        <v>9</v>
+      </c>
+      <c r="C30" s="65">
+        <v>10</v>
+      </c>
+      <c r="D30" s="65">
+        <v>10</v>
+      </c>
+      <c r="E30" s="65">
+        <v>10</v>
+      </c>
+      <c r="F30" s="65">
+        <v>10</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>1</v>
@@ -8200,20 +8237,20 @@
       <c r="A31" s="11">
         <v>15</v>
       </c>
-      <c r="B31" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="C31" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="D31" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="E31" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="F31" s="12" t="s">
-        <v>63</v>
+      <c r="B31" s="65">
+        <v>9</v>
+      </c>
+      <c r="C31" s="65">
+        <v>10</v>
+      </c>
+      <c r="D31" s="65">
+        <v>10</v>
+      </c>
+      <c r="E31" s="65">
+        <v>10</v>
+      </c>
+      <c r="F31" s="65">
+        <v>10</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>1</v>
@@ -8235,20 +8272,20 @@
       <c r="A32" s="11">
         <v>16</v>
       </c>
-      <c r="B32" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="D32" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="E32" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="F32" s="12" t="s">
-        <v>64</v>
+      <c r="B32" s="65">
+        <v>9</v>
+      </c>
+      <c r="C32" s="65">
+        <v>9</v>
+      </c>
+      <c r="D32" s="65">
+        <v>9</v>
+      </c>
+      <c r="E32" s="65">
+        <v>9</v>
+      </c>
+      <c r="F32" s="65">
+        <v>9</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>1</v>
@@ -8270,20 +8307,20 @@
       <c r="A33" s="11">
         <v>17</v>
       </c>
-      <c r="B33" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="C33" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="D33" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="E33" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="F33" s="12" t="s">
-        <v>64</v>
+      <c r="B33" s="65">
+        <v>9</v>
+      </c>
+      <c r="C33" s="65">
+        <v>9</v>
+      </c>
+      <c r="D33" s="65">
+        <v>9</v>
+      </c>
+      <c r="E33" s="65">
+        <v>9</v>
+      </c>
+      <c r="F33" s="65">
+        <v>9</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>1</v>
@@ -8305,20 +8342,20 @@
       <c r="A34" s="11">
         <v>18</v>
       </c>
-      <c r="B34" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="C34" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="D34" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="E34" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="F34" s="12" t="s">
-        <v>64</v>
+      <c r="B34" s="65">
+        <v>9</v>
+      </c>
+      <c r="C34" s="65">
+        <v>9</v>
+      </c>
+      <c r="D34" s="65">
+        <v>9</v>
+      </c>
+      <c r="E34" s="65">
+        <v>9</v>
+      </c>
+      <c r="F34" s="65">
+        <v>9</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>1</v>
@@ -8340,20 +8377,20 @@
       <c r="A35" s="11">
         <v>19</v>
       </c>
-      <c r="B35" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="C35" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="D35" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="E35" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="F35" s="12" t="s">
-        <v>64</v>
+      <c r="B35" s="65">
+        <v>9</v>
+      </c>
+      <c r="C35" s="65">
+        <v>9</v>
+      </c>
+      <c r="D35" s="65">
+        <v>9</v>
+      </c>
+      <c r="E35" s="65">
+        <v>9</v>
+      </c>
+      <c r="F35" s="65">
+        <v>9</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>1</v>
@@ -8752,8 +8789,8 @@
       </c>
     </row>
     <row r="46" ht="16.5" spans="1:11">
-      <c r="A46" s="7" t="s">
-        <v>63</v>
+      <c r="A46" s="64">
+        <v>10</v>
       </c>
       <c r="B46" s="11">
         <f t="shared" si="0"/>
@@ -8792,8 +8829,8 @@
       </c>
     </row>
     <row r="47" ht="16.5" spans="1:11">
-      <c r="A47" s="7" t="s">
-        <v>64</v>
+      <c r="A47" s="64">
+        <v>9</v>
       </c>
       <c r="B47" s="11">
         <f t="shared" si="0"/>
@@ -9958,8 +9995,8 @@
       </c>
     </row>
     <row r="77" ht="16.5" spans="1:11">
-      <c r="A77" s="7" t="s">
-        <v>63</v>
+      <c r="A77" s="64">
+        <v>10</v>
       </c>
       <c r="B77" s="7">
         <v>5</v>
@@ -9997,8 +10034,8 @@
       </c>
     </row>
     <row r="78" ht="16.5" spans="1:11">
-      <c r="A78" s="7" t="s">
-        <v>63</v>
+      <c r="A78" s="64">
+        <v>10</v>
       </c>
       <c r="B78" s="7">
         <v>4</v>
@@ -10036,8 +10073,8 @@
       </c>
     </row>
     <row r="79" ht="16.5" spans="1:11">
-      <c r="A79" s="7" t="s">
-        <v>63</v>
+      <c r="A79" s="64">
+        <v>10</v>
       </c>
       <c r="B79" s="7">
         <v>3</v>
@@ -10075,8 +10112,8 @@
       </c>
     </row>
     <row r="80" ht="16.5" spans="1:11">
-      <c r="A80" s="7" t="s">
-        <v>64</v>
+      <c r="A80" s="64">
+        <v>9</v>
       </c>
       <c r="B80" s="7">
         <v>5</v>
@@ -10114,8 +10151,8 @@
       </c>
     </row>
     <row r="81" ht="16.5" spans="1:11">
-      <c r="A81" s="7" t="s">
-        <v>64</v>
+      <c r="A81" s="64">
+        <v>9</v>
       </c>
       <c r="B81" s="7">
         <v>4</v>
@@ -10153,8 +10190,8 @@
       </c>
     </row>
     <row r="82" ht="16.5" spans="1:11">
-      <c r="A82" s="7" t="s">
-        <v>64</v>
+      <c r="A82" s="64">
+        <v>9</v>
       </c>
       <c r="B82" s="7">
         <v>3</v>
@@ -11384,8 +11421,8 @@
       <c r="A115" s="11">
         <v>9</v>
       </c>
-      <c r="B115" s="12" t="s">
-        <v>63</v>
+      <c r="B115" s="65">
+        <v>10</v>
       </c>
       <c r="C115" s="12" t="s">
         <v>60</v>
@@ -11419,8 +11456,8 @@
       <c r="A116" s="11">
         <v>10</v>
       </c>
-      <c r="B116" s="12" t="s">
-        <v>63</v>
+      <c r="B116" s="65">
+        <v>10</v>
       </c>
       <c r="C116" s="12" t="s">
         <v>60</v>
@@ -11454,8 +11491,8 @@
       <c r="A117" s="11">
         <v>11</v>
       </c>
-      <c r="B117" s="12" t="s">
-        <v>63</v>
+      <c r="B117" s="65">
+        <v>10</v>
       </c>
       <c r="C117" s="12" t="s">
         <v>60</v>
@@ -11489,20 +11526,20 @@
       <c r="A118" s="11">
         <v>12</v>
       </c>
-      <c r="B118" s="12" t="s">
-        <v>63</v>
+      <c r="B118" s="65">
+        <v>10</v>
       </c>
       <c r="C118" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="D118" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="E118" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="F118" s="12" t="s">
-        <v>63</v>
+      <c r="D118" s="65">
+        <v>10</v>
+      </c>
+      <c r="E118" s="65">
+        <v>10</v>
+      </c>
+      <c r="F118" s="65">
+        <v>10</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>1</v>
@@ -11524,20 +11561,20 @@
       <c r="A119" s="11">
         <v>13</v>
       </c>
-      <c r="B119" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="C119" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="D119" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="E119" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="F119" s="12" t="s">
-        <v>63</v>
+      <c r="B119" s="65">
+        <v>10</v>
+      </c>
+      <c r="C119" s="65">
+        <v>10</v>
+      </c>
+      <c r="D119" s="65">
+        <v>10</v>
+      </c>
+      <c r="E119" s="65">
+        <v>10</v>
+      </c>
+      <c r="F119" s="65">
+        <v>10</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>1</v>
@@ -11559,20 +11596,20 @@
       <c r="A120" s="11">
         <v>14</v>
       </c>
-      <c r="B120" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="C120" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="D120" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="E120" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="F120" s="12" t="s">
-        <v>63</v>
+      <c r="B120" s="65">
+        <v>9</v>
+      </c>
+      <c r="C120" s="65">
+        <v>10</v>
+      </c>
+      <c r="D120" s="65">
+        <v>10</v>
+      </c>
+      <c r="E120" s="65">
+        <v>10</v>
+      </c>
+      <c r="F120" s="65">
+        <v>10</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>1</v>
@@ -11594,20 +11631,20 @@
       <c r="A121" s="11">
         <v>15</v>
       </c>
-      <c r="B121" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="C121" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="D121" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="E121" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="F121" s="12" t="s">
-        <v>63</v>
+      <c r="B121" s="65">
+        <v>9</v>
+      </c>
+      <c r="C121" s="65">
+        <v>10</v>
+      </c>
+      <c r="D121" s="65">
+        <v>10</v>
+      </c>
+      <c r="E121" s="65">
+        <v>10</v>
+      </c>
+      <c r="F121" s="65">
+        <v>10</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>1</v>
@@ -11629,20 +11666,20 @@
       <c r="A122" s="11">
         <v>16</v>
       </c>
-      <c r="B122" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="C122" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="D122" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="E122" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="F122" s="12" t="s">
-        <v>64</v>
+      <c r="B122" s="65">
+        <v>9</v>
+      </c>
+      <c r="C122" s="65">
+        <v>9</v>
+      </c>
+      <c r="D122" s="65">
+        <v>9</v>
+      </c>
+      <c r="E122" s="65">
+        <v>9</v>
+      </c>
+      <c r="F122" s="65">
+        <v>9</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>1</v>
@@ -11664,20 +11701,20 @@
       <c r="A123" s="11">
         <v>17</v>
       </c>
-      <c r="B123" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="C123" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="D123" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="E123" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="F123" s="12" t="s">
-        <v>64</v>
+      <c r="B123" s="65">
+        <v>9</v>
+      </c>
+      <c r="C123" s="65">
+        <v>9</v>
+      </c>
+      <c r="D123" s="65">
+        <v>9</v>
+      </c>
+      <c r="E123" s="65">
+        <v>9</v>
+      </c>
+      <c r="F123" s="65">
+        <v>9</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>1</v>
@@ -11699,20 +11736,20 @@
       <c r="A124" s="11">
         <v>18</v>
       </c>
-      <c r="B124" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="C124" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="D124" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="E124" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="F124" s="12" t="s">
-        <v>64</v>
+      <c r="B124" s="65">
+        <v>9</v>
+      </c>
+      <c r="C124" s="65">
+        <v>9</v>
+      </c>
+      <c r="D124" s="65">
+        <v>9</v>
+      </c>
+      <c r="E124" s="65">
+        <v>9</v>
+      </c>
+      <c r="F124" s="65">
+        <v>9</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>1</v>
@@ -11734,17 +11771,17 @@
       <c r="A125" s="11">
         <v>19</v>
       </c>
-      <c r="B125" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="C125" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="D125" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="E125" s="12" t="s">
-        <v>64</v>
+      <c r="B125" s="65">
+        <v>9</v>
+      </c>
+      <c r="C125" s="65">
+        <v>9</v>
+      </c>
+      <c r="D125" s="65">
+        <v>9</v>
+      </c>
+      <c r="E125" s="65">
+        <v>9</v>
       </c>
       <c r="F125" s="12" t="s">
         <v>66</v>
@@ -12146,8 +12183,8 @@
       </c>
     </row>
     <row r="136" ht="16.5" spans="1:11">
-      <c r="A136" s="7" t="s">
-        <v>63</v>
+      <c r="A136" s="64">
+        <v>10</v>
       </c>
       <c r="B136" s="11">
         <f t="shared" si="9"/>
@@ -12186,8 +12223,8 @@
       </c>
     </row>
     <row r="137" ht="16.5" spans="1:11">
-      <c r="A137" s="7" t="s">
-        <v>64</v>
+      <c r="A137" s="64">
+        <v>9</v>
       </c>
       <c r="B137" s="11">
         <f t="shared" si="9"/>
@@ -13352,8 +13389,8 @@
       </c>
     </row>
     <row r="167" ht="16.5" spans="1:11">
-      <c r="A167" s="7" t="s">
-        <v>63</v>
+      <c r="A167" s="64">
+        <v>10</v>
       </c>
       <c r="B167" s="7">
         <v>5</v>
@@ -13391,8 +13428,8 @@
       </c>
     </row>
     <row r="168" ht="16.5" spans="1:11">
-      <c r="A168" s="7" t="s">
-        <v>63</v>
+      <c r="A168" s="64">
+        <v>10</v>
       </c>
       <c r="B168" s="7">
         <v>4</v>
@@ -13430,8 +13467,8 @@
       </c>
     </row>
     <row r="169" ht="16.5" spans="1:11">
-      <c r="A169" s="7" t="s">
-        <v>63</v>
+      <c r="A169" s="64">
+        <v>10</v>
       </c>
       <c r="B169" s="7">
         <v>3</v>
@@ -13469,8 +13506,8 @@
       </c>
     </row>
     <row r="170" ht="16.5" spans="1:11">
-      <c r="A170" s="7" t="s">
-        <v>64</v>
+      <c r="A170" s="64">
+        <v>9</v>
       </c>
       <c r="B170" s="7">
         <v>5</v>
@@ -13508,8 +13545,8 @@
       </c>
     </row>
     <row r="171" ht="16.5" spans="1:11">
-      <c r="A171" s="7" t="s">
-        <v>64</v>
+      <c r="A171" s="64">
+        <v>9</v>
       </c>
       <c r="B171" s="7">
         <v>4</v>
@@ -13547,8 +13584,8 @@
       </c>
     </row>
     <row r="172" ht="16.5" spans="1:11">
-      <c r="A172" s="7" t="s">
-        <v>64</v>
+      <c r="A172" s="64">
+        <v>9</v>
       </c>
       <c r="B172" s="7">
         <v>3</v>
